--- a/usd-futures-curve-analyzer-matba-rofex/holidays.xlsx
+++ b/usd-futures-curve-analyzer-matba-rofex/holidays.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlos.e.maccarrone\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195E7C68-6F68-4867-A3C3-36F754BCD267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5E9024-ADB7-4B09-A523-C086ED5E7953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>Fecha</t>
   </si>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>Noche buena</t>
+  </si>
+  <si>
+    <t>Dia del veterano de malvinas</t>
+  </si>
+  <si>
+    <t>Paso a la inmortalidad Gra. Martin Guemes</t>
   </si>
 </sst>
 </file>
@@ -86,7 +92,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -119,7 +125,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" style="1" bestFit="1" customWidth="1"/>
@@ -584,6 +590,86 @@
         <v>2</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>46426</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>46427</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>46470</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>46472</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>46479</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>46532</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>46555</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>46577</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>46616</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>46672</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
